--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="138">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-care-plan.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-care-plan.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-care-plan.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-care-plan.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-care-plan.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-care-plan.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-care-plan.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -752,7 +756,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1717,13 +1721,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1774,7 +1778,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1791,10 +1795,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1817,13 +1821,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1874,7 +1878,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1891,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1917,13 +1921,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1974,7 +1978,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1991,10 +1995,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2017,13 +2021,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2074,7 +2078,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2091,10 +2095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2117,13 +2121,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2174,7 +2178,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2191,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2217,13 +2221,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2274,7 +2278,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2291,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2317,13 +2321,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2374,7 +2378,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2391,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2417,13 +2421,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2474,7 +2478,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2491,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2517,13 +2521,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2574,7 +2578,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2591,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2617,13 +2621,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2674,7 +2678,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-care-plan.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-care-plan.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-care-plan.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-care-plan.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-care-plan.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-care-plan.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-care-plan.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-care-plan.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-care-plan.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-care-plan.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-care-plan.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,29 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-care-plan.header.source</t>
+    <t>fr-lm-care-plan.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut du plan de soin (projet, actif, suspendu, annulé, terminé, erreur, inconnu)</t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-care-plan.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -410,12 +455,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-care-plan.status</t>
-  </si>
-  <si>
-    <t>Statut du plan de soin (projet, actif, suspendu, annulé, terminé, erreur, inconnu)</t>
   </si>
   <si>
     <t>fr-lm-care-plan.addresses</t>
@@ -743,11 +782,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.21875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.21875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.9296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -756,7 +795,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -770,14 +809,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.97265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1521,13 +1560,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1578,7 +1617,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1595,10 +1634,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1621,13 +1660,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1678,7 +1717,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1695,10 +1734,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1721,13 +1760,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1778,7 +1817,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1795,10 +1834,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1821,7 +1860,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -1921,13 +1960,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1978,7 +2017,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1995,10 +2034,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2009,7 +2048,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2021,13 +2060,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2078,13 +2117,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2095,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2109,7 +2148,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2121,13 +2160,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2178,13 +2217,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2195,10 +2234,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2209,7 +2248,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2221,13 +2260,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2278,13 +2317,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2295,10 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2306,7 +2345,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2321,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2378,10 +2417,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2406,10 +2445,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -2427,7 +2466,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2457,10 +2496,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2478,13 +2517,13 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>73</v>
@@ -2495,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2509,7 +2548,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
@@ -2521,13 +2560,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2578,13 +2617,13 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>73</v>
@@ -2595,10 +2634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2609,7 +2648,7 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2621,13 +2660,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2678,18 +2717,318 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AI19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-care-plan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
